--- a/patient_import_template.xlsx
+++ b/patient_import_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>First Name</t>
   </si>
@@ -118,31 +118,28 @@
     <t>Male</t>
   </si>
   <si>
-    <t>Exe</t>
-  </si>
-  <si>
-    <t>Masm Exe</t>
-  </si>
-  <si>
-    <t>Fred Pemphero</t>
-  </si>
-  <si>
-    <t>Balakasi</t>
-  </si>
-  <si>
-    <t>Masm 2600526</t>
-  </si>
-  <si>
-    <t>Tamanda</t>
-  </si>
-  <si>
-    <t>Masm 2600526-1</t>
-  </si>
-  <si>
-    <t>Masm 2600526-2</t>
-  </si>
-  <si>
-    <t>Mwayi Ken</t>
+    <t>Masm Vip</t>
+  </si>
+  <si>
+    <t>Vip</t>
+  </si>
+  <si>
+    <t>Divyakant</t>
+  </si>
+  <si>
+    <t>Smita-Seema</t>
+  </si>
+  <si>
+    <t>Amin</t>
+  </si>
+  <si>
+    <t>Box  5003 LB</t>
+  </si>
+  <si>
+    <t>Masm 900016436</t>
+  </si>
+  <si>
+    <t>Masm 900016436-1</t>
   </si>
 </sst>
 </file>
@@ -596,111 +593,82 @@
       <c r="A2" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>35</v>
+      <c r="B2" t="s">
+        <v>36</v>
       </c>
       <c r="C2" s="5"/>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="2">
-        <v>9953133554</v>
-      </c>
-      <c r="G2" s="4"/>
-      <c r="K2" s="4" t="s">
+      <c r="E2" s="2"/>
+      <c r="G2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="M2" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="G3" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2">
-        <v>9953133554</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="K3" s="4" t="s">
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>38</v>
+      <c r="M3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="4" t="s">
-        <v>31</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="D4" s="5"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="4"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="K5" s="4"/>
+      <c r="D5" s="5"/>
       <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="K6" s="4"/>
+      <c r="D6" s="5"/>
       <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="K7" s="4"/>
+      <c r="D7" s="2"/>
       <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="D8" s="4"/>
       <c r="G8" s="4"/>
-      <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>

--- a/patient_import_template.xlsx
+++ b/patient_import_template.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>First Name</t>
   </si>
@@ -73,13 +73,22 @@
     <t>Scheme Number</t>
   </si>
   <si>
-    <t>MPHATSO</t>
-  </si>
-  <si>
-    <t>KAMZINGENI ZULU</t>
-  </si>
-  <si>
-    <t>MALE</t>
+    <t>LIZZIE BESITALA</t>
+  </si>
+  <si>
+    <t>KUNJE</t>
+  </si>
+  <si>
+    <t>18/06/1945</t>
+  </si>
+  <si>
+    <t>FEMALE</t>
+  </si>
+  <si>
+    <t>(0)999959105/0997085919</t>
+  </si>
+  <si>
+    <t>BT</t>
   </si>
   <si>
     <t>Masm Vip</t>
@@ -88,25 +97,7 @@
     <t>Vip</t>
   </si>
   <si>
-    <t>Masm 900017236</t>
-  </si>
-  <si>
-    <t>PEMPHERO</t>
-  </si>
-  <si>
-    <t>Masm 900017236-1</t>
-  </si>
-  <si>
-    <t>CATRICE</t>
-  </si>
-  <si>
-    <t>KAWOLOKA</t>
-  </si>
-  <si>
-    <t>FEMALE</t>
-  </si>
-  <si>
-    <t>Masm 900017236-2</t>
+    <t>Masm 970081912</t>
   </si>
   <si>
     <t>PATIENT IMPORT TEMPLATE INSTRUCTIONS</t>
@@ -260,7 +251,7 @@
     <xf numFmtId="42" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -294,6 +285,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -488,75 +480,50 @@
       <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13"/>
+      <c r="C2" s="13" t="s">
+        <v>15</v>
+      </c>
       <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="G2" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" ht="15">
-      <c r="A3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5"/>
+      <c r="C3" s="15"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
-      <c r="K3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" ht="15">
-      <c r="A4" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
+      <c r="M3" s="4"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14"/>
       <c r="C4" s="13"/>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
-      <c r="K4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="M4" s="4"/>
     </row>
     <row r="5">
       <c r="C5" s="13"/>
@@ -618,7 +585,7 @@
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
     </row>
-    <row r="14" ht="14.25">
+    <row r="14">
       <c r="A14" s="7"/>
       <c r="B14" s="10"/>
       <c r="D14" s="7"/>
@@ -826,87 +793,87 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" s="12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" ht="14.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" ht="14.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="14.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="14.25">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" ht="14.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" ht="14.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" ht="14.25">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" ht="14.25">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" ht="14.25">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" ht="14.25">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
